--- a/se216_softwareProcessModel_Group7.xlsx
+++ b/se216_softwareProcessModel_Group7.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="9060" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="ProductBackLog" sheetId="4" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="95">
   <si>
     <r>
       <rPr>
@@ -210,12 +210,6 @@
     <t>Make sure bussinesses, users, and the city have their own private login/registration screens and profiles.</t>
   </si>
   <si>
-    <t>Designing the system with a modular architecture for future AI prediction updates.</t>
-  </si>
-  <si>
-    <t>Adopt a modular monolith or microservices approach. Create clean interfaces for the pricing and recommendation modules so AI models can easily replace rule-based logic later.</t>
-  </si>
-  <si>
     <t>Implementation of AES-256 encryption and SSL/TLS protocols for all user/payment data</t>
   </si>
   <si>
@@ -279,7 +273,7 @@
     <t>Implementation of a two-stage redistribution model (auto-transfer to municipalities).</t>
   </si>
   <si>
-    <t>Create automated CRON jobs that scan for expired user-pickup times and automatically flag the items for municipal transfer.</t>
+    <t>Create modules that scan for expired user-pickup times and automatically flag the items for municipal transfer.</t>
   </si>
   <si>
     <t>Development of a municipal management panel to track  incoming transfers and process user pickups.</t>
@@ -298,6 +292,12 @@
   </si>
   <si>
     <t>User should be able to make donations by sending donations or by purchasing food/supplies</t>
+  </si>
+  <si>
+    <t>Designing the system with a modular architecture for future AI prediction updates.</t>
+  </si>
+  <si>
+    <t>Create clean system architecture for the pricing and recommendation modules so AI models can easily replace rule-based logic later.</t>
   </si>
   <si>
     <t>SPRINT-4</t>
@@ -321,13 +321,13 @@
     <t>Business owner shall be regularly receiving updates on the product thats getting close to expire throughout the 24 hours</t>
   </si>
   <si>
-    <t>Optimization of the application for Android 10+ and iOS 14+ on 4GB RAM devices.</t>
+    <t>Test optimization of the application for Android 10+ and iOS 14+ on 4GB RAM devices.</t>
   </si>
   <si>
-    <t xml:space="preserve">Make sure the app runs smoothly even on devices that fulfill only the minimal requirements and make sure it runs compatible with all devices </t>
+    <t xml:space="preserve">Test if the app runs smoothly even on devices that fulfill only the minimal requirements and make sure it runs compatible with all devices </t>
   </si>
   <si>
-    <t>Ensuring the system supports 10,000 concurrent users with 3s response times.</t>
+    <t>Testing if the system supports 10,000 concurrent users with 3s response times.</t>
   </si>
   <si>
     <t>Test the app to stay fast even when thousands of people use it at once.</t>
@@ -337,6 +337,13 @@
   </si>
   <si>
     <t>Save a copy of all data every day and make a plan to restart quickly if it crashes.</t>
+  </si>
+  <si>
+    <t>Testing for Security Concerns</t>
+  </si>
+  <si>
+    <t>Run tests to see how well the system is designed 
+without security vulnerabilities or exploits.</t>
   </si>
   <si>
     <t>KEY DROPDOWNS - DO NOT DELETE</t>
@@ -1482,7 +1489,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1692,8 +1699,20 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1703,9 +1722,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1787,7 +1803,21 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.599963377788629"/>
+          <bgColor theme="5" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0" tint="-0.249946592608417"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1801,28 +1831,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="5"/>
+          <bgColor theme="5" tint="0.599963377788629"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="0" tint="-0.249946592608417"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FF94EFFB"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1836,7 +1852,7 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FF94EFFB"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1891,13 +1907,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>555625</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>261620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1501775</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>57785</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
@@ -1907,7 +1923,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7652385" y="8719820"/>
+          <a:off x="7652385" y="7576820"/>
           <a:ext cx="3684270" cy="1764665"/>
         </a:xfrm>
         <a:prstGeom prst="snip1Rect">
@@ -2129,13 +2145,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>179070</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>240030</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1169670</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>172720</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
@@ -2145,7 +2161,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10013950" y="9549130"/>
+          <a:off x="10013950" y="8406130"/>
           <a:ext cx="990600" cy="770890"/>
         </a:xfrm>
         <a:custGeom>
@@ -2414,12 +2430,12 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="tr-TR" altLang="en-US" sz="900" b="1">
+            <a:rPr lang="tr-TR" altLang="en-US" sz="1100" b="1">
               <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Front-End Dev</a:t>
+            <a:t>DEV 1</a:t>
           </a:r>
-          <a:endParaRPr lang="tr-TR" altLang="en-US" sz="900" b="1">
+          <a:endParaRPr lang="tr-TR" altLang="en-US" sz="1100" b="1">
             <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
           </a:endParaRPr>
         </a:p>
@@ -2431,13 +2447,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>2130425</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>475615</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>270510</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>66040</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
@@ -2447,7 +2463,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11965305" y="8933815"/>
+          <a:off x="11965305" y="7790815"/>
           <a:ext cx="3253105" cy="1558925"/>
         </a:xfrm>
         <a:prstGeom prst="snip1Rect">
@@ -2648,13 +2664,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>493395</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>250825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>173355</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>222250</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
@@ -2664,7 +2680,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14379575" y="9559925"/>
+          <a:off x="14379575" y="8416925"/>
           <a:ext cx="741680" cy="809625"/>
         </a:xfrm>
         <a:custGeom>
@@ -2938,7 +2954,7 @@
             <a:rPr lang="tr-TR" altLang="en-US" sz="900" b="1">
               <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Data Engineer</a:t>
+            <a:t>DEV 2</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR" altLang="en-US" sz="900" b="1">
             <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
@@ -2952,13 +2968,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>532765</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>367665</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>243205</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>273050</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
@@ -2968,7 +2984,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15480665" y="8825865"/>
+          <a:off x="15480665" y="7682865"/>
           <a:ext cx="3831590" cy="1873885"/>
         </a:xfrm>
         <a:prstGeom prst="snip1Rect">
@@ -3115,7 +3131,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>As a user I want my personal data and payment information to be protected by AES-256 encryption, so that I can rescue food and support my community with total peace of mind, knowing that even the data of high-level authorities using the system is kept behind military-grade security.</a:t>
+            <a:t>As a user I want my personal data and payment information to be protected well so that I can rescue food and support my community with total peace of mind, knowing that my data is safe and secure.</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR" altLang="en-US" sz="1100" kern="1200" baseline="0">
             <a:solidFill>
@@ -3157,15 +3173,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>386715</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>205740</xdr:rowOff>
+      <xdr:colOff>128905</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>237490</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>360680</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>41910</xdr:rowOff>
+      <xdr:colOff>102870</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>73660</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -3174,7 +3190,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18394045" y="10073640"/>
+          <a:off x="18136235" y="8682990"/>
           <a:ext cx="1035685" cy="953770"/>
         </a:xfrm>
         <a:custGeom>
@@ -3445,12 +3461,12 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="tr-TR" altLang="en-US" sz="900" b="1">
+            <a:rPr lang="tr-TR" altLang="en-US" sz="1600" b="1">
               <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Cybersecurity Lead</a:t>
+            <a:t>Dev 3</a:t>
           </a:r>
-          <a:endParaRPr lang="tr-TR" altLang="en-US" sz="900" b="1">
+          <a:endParaRPr lang="tr-TR" altLang="en-US" sz="1600" b="1">
             <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
           </a:endParaRPr>
         </a:p>
@@ -4198,7 +4214,7 @@
             <a:rPr lang="tr-TR" altLang="en-US" sz="1100" b="1">
               <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Backend Dev</a:t>
+            <a:t>DEV 1</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR" altLang="en-US" sz="1100" b="1">
             <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
@@ -4749,21 +4765,9 @@
             <a:rPr lang="tr-TR" altLang="en-US" sz="1100" b="1">
               <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Backend</a:t>
+            <a:t>DEV 5</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR" altLang="en-US" sz="1100" b="1">
-            <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1">
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Dev</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" b="1">
             <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
           </a:endParaRPr>
         </a:p>
@@ -5063,7 +5067,7 @@
             <a:rPr lang="tr-TR" altLang="en-US" sz="1100" b="1">
               <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Backend Dev</a:t>
+            <a:t>DEV 1</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR" altLang="en-US" sz="1100" b="1">
             <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
@@ -5553,7 +5557,7 @@
             <a:rPr lang="tr-TR" sz="1100" b="1">
               <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Frontend Dev</a:t>
+            <a:t>DEV 2</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR" sz="1100" b="1">
             <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
@@ -5588,7 +5592,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7102475" y="9657715"/>
+          <a:off x="7102475" y="10546715"/>
           <a:ext cx="3208020" cy="1734185"/>
         </a:xfrm>
         <a:prstGeom prst="snip1Rect">
@@ -5817,7 +5821,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10915015" y="10055225"/>
+          <a:off x="10915015" y="10944225"/>
           <a:ext cx="3550285" cy="1597660"/>
         </a:xfrm>
         <a:prstGeom prst="snip1Rect">
@@ -6045,7 +6049,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9295130" y="10880725"/>
+          <a:off x="9295130" y="11769725"/>
           <a:ext cx="807085" cy="776605"/>
         </a:xfrm>
         <a:custGeom>
@@ -6317,7 +6321,7 @@
             <a:rPr lang="tr-TR" altLang="en-US" sz="900" b="1">
               <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Backend Dev</a:t>
+            <a:t>DEV 4</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR" altLang="en-US" sz="900" b="1">
             <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
@@ -6347,7 +6351,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13156565" y="10857865"/>
+          <a:off x="13156565" y="11746865"/>
           <a:ext cx="1042670" cy="956945"/>
         </a:xfrm>
         <a:custGeom>
@@ -6619,7 +6623,7 @@
             <a:rPr lang="tr-TR" altLang="en-US" sz="900" b="1">
               <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Cybersecurity Lead</a:t>
+            <a:t>DEV 3</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR" altLang="en-US" sz="900" b="1">
             <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
@@ -6649,7 +6653,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15126335" y="10096500"/>
+          <a:off x="15126335" y="10985500"/>
           <a:ext cx="3550285" cy="1597660"/>
         </a:xfrm>
         <a:prstGeom prst="snip1Rect">
@@ -6866,7 +6870,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17457420" y="10920095"/>
+          <a:off x="17457420" y="11809095"/>
           <a:ext cx="818515" cy="834390"/>
         </a:xfrm>
         <a:custGeom>
@@ -7138,7 +7142,7 @@
             <a:rPr lang="tr-TR" altLang="en-US" sz="900" b="1">
               <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t> Backend Dev</a:t>
+            <a:t>DEV 4</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR" altLang="en-US" sz="900" b="1">
             <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
@@ -7156,13 +7160,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>418465</xdr:colOff>
+      <xdr:colOff>464820</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>136525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>358140</xdr:colOff>
+      <xdr:colOff>404495</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>207645</xdr:rowOff>
     </xdr:to>
@@ -7173,7 +7177,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6914515" y="8886825"/>
+          <a:off x="6960870" y="9293225"/>
           <a:ext cx="2677795" cy="1480820"/>
         </a:xfrm>
         <a:prstGeom prst="snip1Rect">
@@ -7367,7 +7371,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9844405" y="9362440"/>
+          <a:off x="9844405" y="9768840"/>
           <a:ext cx="2578735" cy="1381760"/>
         </a:xfrm>
         <a:prstGeom prst="snip1Rect">
@@ -7584,7 +7588,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11636375" y="10368915"/>
+          <a:off x="11636375" y="10775315"/>
           <a:ext cx="748665" cy="659130"/>
         </a:xfrm>
         <a:custGeom>
@@ -7856,7 +7860,7 @@
             <a:rPr lang="tr-TR" altLang="en-US" sz="900" b="1">
               <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Data Analyst</a:t>
+            <a:t>DEV 5</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR" altLang="en-US" sz="900" b="1">
             <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
@@ -7886,7 +7890,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8459470" y="9679940"/>
+          <a:off x="8459470" y="10086340"/>
           <a:ext cx="891540" cy="879475"/>
         </a:xfrm>
         <a:custGeom>
@@ -8155,18 +8159,12 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="en-US" sz="900" b="1">
+            <a:rPr lang="tr-TR" sz="900" b="1">
               <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Dev</a:t>
+            <a:t>DEV 6</a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="tr-TR" altLang="en-US" sz="900" b="1">
-              <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>Ops Engineer</a:t>
-          </a:r>
-          <a:endParaRPr lang="tr-TR" altLang="en-US" sz="900" b="1">
+          <a:endParaRPr lang="tr-TR" sz="900" b="1">
             <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
           </a:endParaRPr>
         </a:p>
@@ -8177,15 +8175,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1066800</xdr:colOff>
+      <xdr:colOff>1066165</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>304800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>908050</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
+      <xdr:colOff>1283335</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8194,8 +8192,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13039090" y="9055100"/>
-          <a:ext cx="2216150" cy="1231900"/>
+          <a:off x="13038455" y="9461500"/>
+          <a:ext cx="2592070" cy="1445260"/>
         </a:xfrm>
         <a:prstGeom prst="snip1Rect">
           <a:avLst/>
@@ -8332,7 +8330,7 @@
         </a:lstStyle>
         <a:p>
           <a:r>
-            <a:rPr lang="tr-TR" sz="800" b="0">
+            <a:rPr lang="tr-TR" sz="1000" b="0">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
@@ -8340,7 +8338,7 @@
             </a:rPr>
             <a:t>AS a business owner , I would want to be notified whenever there is short (24 hrs )time left before my product expires so it can be make it to good hands in time.</a:t>
           </a:r>
-          <a:endParaRPr lang="tr-TR" sz="800" b="0">
+          <a:endParaRPr lang="tr-TR" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="tx1"/>
             </a:solidFill>
@@ -8349,7 +8347,7 @@
         </a:p>
         <a:p>
           <a:pPr marL="0" indent="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1"/>
-          <a:endParaRPr lang="en-US" sz="800" kern="1200" baseline="0">
+          <a:endParaRPr lang="en-US" sz="1000" kern="1200" baseline="0">
             <a:solidFill>
               <a:schemeClr val="tx1"/>
             </a:solidFill>
@@ -8361,7 +8359,7 @@
         </a:p>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="800" kern="1200" baseline="0">
+            <a:rPr lang="en-US" sz="1000" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
@@ -8372,7 +8370,7 @@
             </a:rPr>
             <a:t>STATUS: Not Started</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="800" kern="1200" baseline="0">
+          <a:endParaRPr lang="en-US" sz="1000" kern="1200" baseline="0">
             <a:solidFill>
               <a:schemeClr val="tx1"/>
             </a:solidFill>
@@ -8383,7 +8381,7 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:endParaRPr lang="en-US" sz="800">
+          <a:endParaRPr lang="en-US" sz="1000">
             <a:solidFill>
               <a:schemeClr val="tx1"/>
             </a:solidFill>
@@ -8398,15 +8396,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>208280</xdr:colOff>
+      <xdr:colOff>292100</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>218440</xdr:rowOff>
+      <xdr:rowOff>255905</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>937260</xdr:colOff>
+      <xdr:colOff>1021080</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>151765</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -8415,7 +8413,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14555470" y="9819640"/>
+          <a:off x="14639290" y="10263505"/>
           <a:ext cx="728980" cy="734060"/>
         </a:xfrm>
         <a:custGeom>
@@ -8687,7 +8685,7 @@
             <a:rPr lang="tr-TR" altLang="en-US" sz="900" b="1">
               <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
-            <a:t>Backend Dev</a:t>
+            <a:t>DEV 1</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR" altLang="en-US" sz="900" b="1">
             <a:latin typeface="Century Gothic" panose="020B0502020202020204" pitchFamily="34" charset="0"/>
@@ -16559,176 +16557,176 @@
   </cols>
   <sheetData>
     <row r="1" ht="92" customHeight="1" spans="1:2">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="91"/>
+      <c r="B1" s="94"/>
     </row>
     <row r="2" ht="45" customHeight="1" spans="1:2">
-      <c r="A2" s="92" t="s">
+      <c r="A2" s="95" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="92" t="s">
+      <c r="B2" s="95" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" ht="45" customHeight="1" spans="1:2">
-      <c r="A3" s="92">
+      <c r="A3" s="95">
         <v>1</v>
       </c>
-      <c r="B3" s="93" t="s">
+      <c r="B3" s="96" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" ht="45" customHeight="1" spans="1:2">
-      <c r="A4" s="92">
+      <c r="A4" s="95">
         <v>2</v>
       </c>
-      <c r="B4" s="94" t="s">
+      <c r="B4" s="97" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" ht="45" customHeight="1" spans="1:2">
-      <c r="A5" s="92">
+      <c r="A5" s="95">
         <v>3</v>
       </c>
-      <c r="B5" s="94" t="s">
+      <c r="B5" s="97" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1" spans="1:2">
-      <c r="A6" s="92">
+      <c r="A6" s="95">
         <v>4</v>
       </c>
-      <c r="B6" s="94" t="s">
+      <c r="B6" s="97" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1" spans="1:2">
-      <c r="A7" s="92">
+      <c r="A7" s="95">
         <v>5</v>
       </c>
-      <c r="B7" s="94" t="s">
+      <c r="B7" s="97" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1" spans="1:2">
-      <c r="A8" s="92">
+      <c r="A8" s="95">
         <v>6</v>
       </c>
-      <c r="B8" s="94" t="s">
+      <c r="B8" s="97" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" ht="45" customHeight="1" spans="1:2">
-      <c r="A9" s="92">
+      <c r="A9" s="95">
         <v>7</v>
       </c>
-      <c r="B9" s="94" t="s">
+      <c r="B9" s="97" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" ht="45" customHeight="1" spans="1:2">
-      <c r="A10" s="92">
+      <c r="A10" s="95">
         <v>8</v>
       </c>
-      <c r="B10" s="94" t="s">
+      <c r="B10" s="97" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" ht="45" customHeight="1" spans="1:2">
-      <c r="A11" s="92">
+      <c r="A11" s="95">
         <v>9</v>
       </c>
-      <c r="B11" s="94" t="s">
+      <c r="B11" s="97" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12" ht="45" customHeight="1" spans="1:2">
-      <c r="A12" s="92">
+      <c r="A12" s="95">
         <v>10</v>
       </c>
-      <c r="B12" s="94" t="s">
+      <c r="B12" s="97" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="13" ht="45" customHeight="1" spans="1:2">
-      <c r="A13" s="92">
+      <c r="A13" s="95">
         <v>11</v>
       </c>
-      <c r="B13" s="94" t="s">
+      <c r="B13" s="97" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="14" ht="45" customHeight="1" spans="1:2">
-      <c r="A14" s="92">
+      <c r="A14" s="95">
         <v>12</v>
       </c>
-      <c r="B14" s="95" t="s">
+      <c r="B14" s="98" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="15" ht="45" customHeight="1" spans="1:2">
-      <c r="A15" s="92">
+      <c r="A15" s="95">
         <v>13</v>
       </c>
-      <c r="B15" s="95" t="s">
+      <c r="B15" s="98" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" ht="45" customHeight="1" spans="1:2">
-      <c r="A16" s="92">
+      <c r="A16" s="95">
         <v>14</v>
       </c>
-      <c r="B16" s="95" t="s">
+      <c r="B16" s="98" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="17" ht="45" customHeight="1" spans="1:2">
-      <c r="A17" s="92">
+      <c r="A17" s="95">
         <v>15</v>
       </c>
-      <c r="B17" s="95" t="s">
+      <c r="B17" s="98" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="18" ht="45" customHeight="1" spans="1:2">
-      <c r="A18" s="92">
+      <c r="A18" s="95">
         <v>16</v>
       </c>
-      <c r="B18" s="95" t="s">
+      <c r="B18" s="98" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1" spans="1:2">
-      <c r="A19" s="92">
+      <c r="A19" s="95">
         <v>17</v>
       </c>
-      <c r="B19" s="95" t="s">
+      <c r="B19" s="98" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="20" ht="45" customHeight="1" spans="1:2">
-      <c r="A20" s="92">
+      <c r="A20" s="95">
         <v>18</v>
       </c>
-      <c r="B20" s="95" t="s">
+      <c r="B20" s="98" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1" spans="1:2">
-      <c r="A21" s="92">
+      <c r="A21" s="95">
         <v>19</v>
       </c>
-      <c r="B21" s="95" t="s">
+      <c r="B21" s="98" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1" spans="1:2">
-      <c r="A22" s="92">
+      <c r="A22" s="95">
         <v>20</v>
       </c>
-      <c r="B22" s="95" t="s">
+      <c r="B22" s="98" t="s">
         <v>22</v>
       </c>
     </row>
@@ -16745,7 +16743,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:O34"/>
+  <dimension ref="B1:O33"/>
   <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="3.33333333333333" customWidth="1"/>
@@ -16810,10 +16808,10 @@
       <c r="M2" s="76"/>
     </row>
     <row r="3" ht="50" customHeight="1" spans="2:13">
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="88" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="85" t="s">
+      <c r="C3" s="89" t="s">
         <v>33</v>
       </c>
       <c r="D3" s="29" t="s">
@@ -16828,10 +16826,10 @@
       <c r="G3" s="49">
         <v>46695</v>
       </c>
-      <c r="H3" s="86">
+      <c r="H3" s="90">
         <v>4</v>
       </c>
-      <c r="I3" s="88" t="s">
+      <c r="I3" s="91" t="s">
         <v>36</v>
       </c>
       <c r="M3" s="77"/>
@@ -16840,7 +16838,7 @@
       <c r="B4" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="85" t="s">
+      <c r="C4" s="89" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="31" t="s">
@@ -16858,63 +16856,47 @@
       <c r="H4" s="50">
         <v>6</v>
       </c>
-      <c r="I4" s="88" t="s">
+      <c r="I4" s="91" t="s">
         <v>40</v>
       </c>
       <c r="M4" s="77"/>
     </row>
-    <row r="5" ht="90" customHeight="1" spans="2:13">
+    <row r="5" ht="58" customHeight="1" spans="2:13">
       <c r="B5" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="85" t="s">
+      <c r="C5" s="89" t="s">
         <v>41</v>
       </c>
       <c r="D5" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="87" t="s">
+      <c r="E5" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="49">
+      <c r="F5" s="55">
         <v>46692</v>
       </c>
-      <c r="G5" s="49">
-        <v>46696</v>
-      </c>
-      <c r="H5" s="50">
-        <v>5</v>
-      </c>
-      <c r="I5" s="88" t="s">
+      <c r="G5" s="55">
+        <v>46694</v>
+      </c>
+      <c r="H5" s="56">
+        <v>3</v>
+      </c>
+      <c r="I5" s="92" t="s">
         <v>42</v>
       </c>
       <c r="M5" s="77"/>
     </row>
-    <row r="6" ht="58" customHeight="1" spans="2:13">
-      <c r="B6" s="48" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="85" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="55">
-        <v>46692</v>
-      </c>
-      <c r="G6" s="55">
-        <v>46694</v>
-      </c>
-      <c r="H6" s="56">
-        <v>3</v>
-      </c>
-      <c r="I6" s="89" t="s">
-        <v>44</v>
-      </c>
+    <row r="6" ht="22" customHeight="1" spans="2:13">
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="77"/>
       <c r="M6" s="77"/>
     </row>
     <row r="7" ht="22" customHeight="1" spans="2:13">
@@ -16926,6 +16908,604 @@
       <c r="G7" s="55"/>
       <c r="H7" s="56"/>
       <c r="I7" s="77"/>
+      <c r="M7" s="77"/>
+    </row>
+    <row r="8" ht="22" customHeight="1" spans="2:13">
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="55"/>
+      <c r="G8" s="55"/>
+      <c r="H8" s="56"/>
+      <c r="I8" s="77"/>
+      <c r="M8" s="77"/>
+    </row>
+    <row r="9" ht="22" customHeight="1" spans="2:13">
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="77"/>
+      <c r="M9" s="77"/>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="2:13">
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="58"/>
+      <c r="F10" s="55"/>
+      <c r="G10" s="55"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="77"/>
+      <c r="M10" s="77"/>
+    </row>
+    <row r="11" ht="22" customHeight="1" spans="2:13">
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="77"/>
+      <c r="M11" s="77"/>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="2:13">
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="77"/>
+      <c r="M12" s="77"/>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="2:13">
+      <c r="B13" s="54"/>
+      <c r="C13" s="54"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="77"/>
+      <c r="M13" s="77"/>
+    </row>
+    <row r="14" ht="22" customHeight="1" spans="2:13">
+      <c r="B14" s="54"/>
+      <c r="C14" s="54"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="77"/>
+      <c r="M14" s="77"/>
+    </row>
+    <row r="15" ht="22" customHeight="1" spans="2:13">
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="59"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="77"/>
+      <c r="M15" s="77"/>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="2:13">
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="56"/>
+      <c r="I16" s="77"/>
+      <c r="M16" s="77"/>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="2:13">
+      <c r="B17" s="54"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="56"/>
+      <c r="I17" s="77"/>
+      <c r="M17" s="77"/>
+    </row>
+    <row r="18" ht="22" customHeight="1" spans="2:13">
+      <c r="B18" s="54"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="58"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="59"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="77"/>
+      <c r="M18" s="77"/>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="2:13">
+      <c r="B19" s="54"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="56"/>
+      <c r="I19" s="77"/>
+      <c r="M19" s="77"/>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="2:13">
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="59"/>
+      <c r="H20" s="56"/>
+      <c r="I20" s="77"/>
+      <c r="M20" s="77"/>
+    </row>
+    <row r="21" ht="16.8" spans="2:9">
+      <c r="B21" s="60"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="60"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="61"/>
+      <c r="G21" s="61"/>
+      <c r="H21" s="62">
+        <f>MAX(G3:G4)-MIN(F3:F4)+1</f>
+        <v>10</v>
+      </c>
+      <c r="I21" s="60"/>
+    </row>
+    <row r="22" ht="22" customHeight="1"/>
+    <row r="23" ht="45" customHeight="1" spans="2:14">
+      <c r="B23" s="63" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="64"/>
+      <c r="D23" s="65"/>
+      <c r="E23" s="66"/>
+      <c r="F23" s="66"/>
+      <c r="G23" s="66"/>
+      <c r="H23" s="66"/>
+      <c r="I23" s="66"/>
+      <c r="J23" s="66"/>
+      <c r="K23" s="66"/>
+      <c r="L23" s="66"/>
+      <c r="M23" s="66"/>
+      <c r="N23" s="80"/>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="2:14">
+      <c r="B24" s="67"/>
+      <c r="C24" s="68"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70"/>
+      <c r="I24" s="70"/>
+      <c r="J24" s="70"/>
+      <c r="K24" s="70"/>
+      <c r="L24" s="70"/>
+      <c r="M24" s="70"/>
+      <c r="N24" s="81"/>
+    </row>
+    <row r="25" ht="22" customHeight="1" spans="2:14">
+      <c r="B25" s="67"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="70"/>
+      <c r="K25" s="70"/>
+      <c r="L25" s="70"/>
+      <c r="M25" s="70"/>
+      <c r="N25" s="81"/>
+    </row>
+    <row r="26" ht="22" customHeight="1" spans="2:14">
+      <c r="B26" s="67"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="70"/>
+      <c r="K26" s="70"/>
+      <c r="L26" s="70"/>
+      <c r="M26" s="70"/>
+      <c r="N26" s="81"/>
+    </row>
+    <row r="27" ht="22" customHeight="1" spans="2:14">
+      <c r="B27" s="67"/>
+      <c r="C27" s="68"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="70"/>
+      <c r="K27" s="70"/>
+      <c r="L27" s="70"/>
+      <c r="M27" s="70"/>
+      <c r="N27" s="81"/>
+    </row>
+    <row r="28" ht="22" customHeight="1" spans="2:14">
+      <c r="B28" s="67"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="69"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="70"/>
+      <c r="K28" s="70"/>
+      <c r="L28" s="70"/>
+      <c r="M28" s="70"/>
+      <c r="N28" s="81"/>
+    </row>
+    <row r="29" ht="22" customHeight="1" spans="2:14">
+      <c r="B29" s="67"/>
+      <c r="C29" s="68"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="70"/>
+      <c r="K29" s="70"/>
+      <c r="L29" s="70"/>
+      <c r="M29" s="70"/>
+      <c r="N29" s="81"/>
+    </row>
+    <row r="30" ht="22" customHeight="1" spans="2:14">
+      <c r="B30" s="67"/>
+      <c r="C30" s="68"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="70"/>
+      <c r="K30" s="70"/>
+      <c r="L30" s="70"/>
+      <c r="M30" s="70"/>
+      <c r="N30" s="81"/>
+    </row>
+    <row r="31" ht="22" customHeight="1" spans="2:14">
+      <c r="B31" s="67"/>
+      <c r="C31" s="68"/>
+      <c r="D31" s="69"/>
+      <c r="E31" s="70"/>
+      <c r="F31" s="70"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
+      <c r="I31" s="70"/>
+      <c r="J31" s="70"/>
+      <c r="K31" s="70"/>
+      <c r="L31" s="70"/>
+      <c r="M31" s="70"/>
+      <c r="N31" s="81"/>
+    </row>
+    <row r="32" ht="22" customHeight="1" spans="2:14">
+      <c r="B32" s="71"/>
+      <c r="C32" s="72"/>
+      <c r="D32" s="73"/>
+      <c r="E32" s="74"/>
+      <c r="F32" s="74"/>
+      <c r="G32" s="74"/>
+      <c r="H32" s="74"/>
+      <c r="I32" s="74"/>
+      <c r="J32" s="74"/>
+      <c r="K32" s="74"/>
+      <c r="L32" s="74"/>
+      <c r="M32" s="74"/>
+      <c r="N32" s="82"/>
+    </row>
+    <row r="33" ht="22" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B23:D32"/>
+    <mergeCell ref="E23:N32"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D5">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="between" text="Testing">
+      <formula>NOT(ISERROR(SEARCH("Testing",D5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="2" operator="between" text="On Hold">
+      <formula>NOT(ISERROR(SEARCH("On Hold",D5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="3" operator="between" text="Complete">
+      <formula>NOT(ISERROR(SEARCH("Complete",D5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="4" operator="between" text="Ready to Start">
+      <formula>NOT(ISERROR(SEARCH("Ready to Start",D5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="5" operator="between" text="In Progress">
+      <formula>NOT(ISERROR(SEARCH("In Progress",D5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5">
+    <cfRule type="containsText" dxfId="5" priority="6" operator="between" text="Low">
+      <formula>NOT(ISERROR(SEARCH("Low",E5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="7" operator="between" text="Medium">
+      <formula>NOT(ISERROR(SEARCH("Medium",E5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="7" priority="8" operator="between" text="High">
+      <formula>NOT(ISERROR(SEARCH("High",E5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3:D4">
+    <cfRule type="containsText" dxfId="0" priority="9" operator="between" text="Testing">
+      <formula>NOT(ISERROR(SEARCH("Testing",D3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="10" operator="between" text="On Hold">
+      <formula>NOT(ISERROR(SEARCH("On Hold",D3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="11" operator="between" text="Complete">
+      <formula>NOT(ISERROR(SEARCH("Complete",D3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="12" operator="between" text="Ready to Start">
+      <formula>NOT(ISERROR(SEARCH("Ready to Start",D3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="13" operator="between" text="In Progress">
+      <formula>NOT(ISERROR(SEARCH("In Progress",D3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D6:D20">
+    <cfRule type="containsText" dxfId="0" priority="14" operator="between" text="Testing">
+      <formula>NOT(ISERROR(SEARCH("Testing",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="15" operator="between" text="On Hold">
+      <formula>NOT(ISERROR(SEARCH("On Hold",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="16" operator="between" text="Complete">
+      <formula>NOT(ISERROR(SEARCH("Complete",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="17" operator="between" text="Ready to Start">
+      <formula>NOT(ISERROR(SEARCH("Ready to Start",D6)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="18" operator="between" text="In Progress">
+      <formula>NOT(ISERROR(SEARCH("In Progress",D6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:E4;E6:E20">
+    <cfRule type="containsText" dxfId="5" priority="19" operator="between" text="Low">
+      <formula>NOT(ISERROR(SEARCH("Low",E3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="20" operator="between" text="Medium">
+      <formula>NOT(ISERROR(SEARCH("Medium",E3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="7" priority="21" operator="between" text="High">
+      <formula>NOT(ISERROR(SEARCH("High",E3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:O34"/>
+  <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="3.33333333333333" customWidth="1"/>
+    <col min="2" max="2" width="15.6666666666667" customWidth="1"/>
+    <col min="3" max="3" width="35.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="22.8333333333333" customWidth="1"/>
+    <col min="5" max="6" width="32.6666666666667" customWidth="1"/>
+    <col min="7" max="7" width="15.6666666666667" customWidth="1"/>
+    <col min="8" max="8" width="12.6666666666667" customWidth="1"/>
+    <col min="9" max="9" width="49.3333333333333" customWidth="1"/>
+    <col min="10" max="10" width="12.6666666666667" customWidth="1"/>
+    <col min="11" max="11" width="24.1666666666667" customWidth="1"/>
+    <col min="12" max="12" width="25.6666666666667" customWidth="1"/>
+    <col min="13" max="13" width="28.5" customWidth="1"/>
+    <col min="14" max="14" width="42.6666666666667" customWidth="1"/>
+    <col min="15" max="15" width="3.33333333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="27.6" spans="2:15">
+      <c r="B1" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="75"/>
+    </row>
+    <row r="2" ht="27.6" spans="2:13">
+      <c r="B2" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="46" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="46" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" s="76"/>
+    </row>
+    <row r="3" ht="61" customHeight="1" spans="2:13">
+      <c r="B3" s="48" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="49">
+        <v>46706</v>
+      </c>
+      <c r="G3" s="49">
+        <v>46709</v>
+      </c>
+      <c r="H3" s="50">
+        <v>4</v>
+      </c>
+      <c r="I3" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="M3" s="77"/>
+    </row>
+    <row r="4" ht="48" customHeight="1" spans="2:13">
+      <c r="B4" s="48" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="48" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="49">
+        <v>46706</v>
+      </c>
+      <c r="G4" s="49">
+        <v>46710</v>
+      </c>
+      <c r="H4" s="50">
+        <v>5</v>
+      </c>
+      <c r="I4" s="48" t="s">
+        <v>50</v>
+      </c>
+      <c r="M4" s="77"/>
+    </row>
+    <row r="5" ht="54" customHeight="1" spans="2:13">
+      <c r="B5" s="48" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="49">
+        <v>46703</v>
+      </c>
+      <c r="G5" s="49">
+        <v>46709</v>
+      </c>
+      <c r="H5" s="50">
+        <v>5</v>
+      </c>
+      <c r="I5" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="M5" s="77"/>
+    </row>
+    <row r="6" ht="48" customHeight="1" spans="2:13">
+      <c r="B6" s="48" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="48" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="52">
+        <v>46708</v>
+      </c>
+      <c r="G6" s="52">
+        <v>46709</v>
+      </c>
+      <c r="H6" s="53">
+        <v>2</v>
+      </c>
+      <c r="I6" s="78" t="s">
+        <v>54</v>
+      </c>
+      <c r="M6" s="77"/>
+    </row>
+    <row r="7" ht="47" customHeight="1" spans="2:13">
+      <c r="B7" s="48" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="48" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="55">
+        <v>46708</v>
+      </c>
+      <c r="G7" s="55">
+        <v>46709</v>
+      </c>
+      <c r="H7" s="56">
+        <v>2</v>
+      </c>
+      <c r="I7" s="79" t="s">
+        <v>57</v>
+      </c>
       <c r="M7" s="77"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="2:13">
@@ -17091,623 +17671,14 @@
       <c r="G22" s="61"/>
       <c r="H22" s="62">
         <f>MAX(G3:G5)-MIN(F3:F5)+1</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I22" s="60"/>
     </row>
     <row r="23" ht="22" customHeight="1"/>
     <row r="24" ht="45" customHeight="1" spans="2:14">
       <c r="B24" s="63" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" s="64"/>
-      <c r="D24" s="65"/>
-      <c r="E24" s="66"/>
-      <c r="F24" s="66"/>
-      <c r="G24" s="66"/>
-      <c r="H24" s="66"/>
-      <c r="I24" s="66"/>
-      <c r="J24" s="66"/>
-      <c r="K24" s="66"/>
-      <c r="L24" s="66"/>
-      <c r="M24" s="66"/>
-      <c r="N24" s="80"/>
-    </row>
-    <row r="25" ht="22" customHeight="1" spans="2:14">
-      <c r="B25" s="67"/>
-      <c r="C25" s="68"/>
-      <c r="D25" s="69"/>
-      <c r="E25" s="70"/>
-      <c r="F25" s="70"/>
-      <c r="G25" s="70"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="70"/>
-      <c r="J25" s="70"/>
-      <c r="K25" s="70"/>
-      <c r="L25" s="70"/>
-      <c r="M25" s="70"/>
-      <c r="N25" s="81"/>
-    </row>
-    <row r="26" ht="22" customHeight="1" spans="2:14">
-      <c r="B26" s="67"/>
-      <c r="C26" s="68"/>
-      <c r="D26" s="69"/>
-      <c r="E26" s="70"/>
-      <c r="F26" s="70"/>
-      <c r="G26" s="70"/>
-      <c r="H26" s="70"/>
-      <c r="I26" s="70"/>
-      <c r="J26" s="70"/>
-      <c r="K26" s="70"/>
-      <c r="L26" s="70"/>
-      <c r="M26" s="70"/>
-      <c r="N26" s="81"/>
-    </row>
-    <row r="27" ht="22" customHeight="1" spans="2:14">
-      <c r="B27" s="67"/>
-      <c r="C27" s="68"/>
-      <c r="D27" s="69"/>
-      <c r="E27" s="70"/>
-      <c r="F27" s="70"/>
-      <c r="G27" s="70"/>
-      <c r="H27" s="70"/>
-      <c r="I27" s="70"/>
-      <c r="J27" s="70"/>
-      <c r="K27" s="70"/>
-      <c r="L27" s="70"/>
-      <c r="M27" s="70"/>
-      <c r="N27" s="81"/>
-    </row>
-    <row r="28" ht="22" customHeight="1" spans="2:14">
-      <c r="B28" s="67"/>
-      <c r="C28" s="68"/>
-      <c r="D28" s="69"/>
-      <c r="E28" s="70"/>
-      <c r="F28" s="70"/>
-      <c r="G28" s="70"/>
-      <c r="H28" s="70"/>
-      <c r="I28" s="70"/>
-      <c r="J28" s="70"/>
-      <c r="K28" s="70"/>
-      <c r="L28" s="70"/>
-      <c r="M28" s="70"/>
-      <c r="N28" s="81"/>
-    </row>
-    <row r="29" ht="22" customHeight="1" spans="2:14">
-      <c r="B29" s="67"/>
-      <c r="C29" s="68"/>
-      <c r="D29" s="69"/>
-      <c r="E29" s="70"/>
-      <c r="F29" s="70"/>
-      <c r="G29" s="70"/>
-      <c r="H29" s="70"/>
-      <c r="I29" s="70"/>
-      <c r="J29" s="70"/>
-      <c r="K29" s="70"/>
-      <c r="L29" s="70"/>
-      <c r="M29" s="70"/>
-      <c r="N29" s="81"/>
-    </row>
-    <row r="30" ht="22" customHeight="1" spans="2:14">
-      <c r="B30" s="67"/>
-      <c r="C30" s="68"/>
-      <c r="D30" s="69"/>
-      <c r="E30" s="70"/>
-      <c r="F30" s="70"/>
-      <c r="G30" s="70"/>
-      <c r="H30" s="70"/>
-      <c r="I30" s="70"/>
-      <c r="J30" s="70"/>
-      <c r="K30" s="70"/>
-      <c r="L30" s="70"/>
-      <c r="M30" s="70"/>
-      <c r="N30" s="81"/>
-    </row>
-    <row r="31" ht="22" customHeight="1" spans="2:14">
-      <c r="B31" s="67"/>
-      <c r="C31" s="68"/>
-      <c r="D31" s="69"/>
-      <c r="E31" s="70"/>
-      <c r="F31" s="70"/>
-      <c r="G31" s="70"/>
-      <c r="H31" s="70"/>
-      <c r="I31" s="70"/>
-      <c r="J31" s="70"/>
-      <c r="K31" s="70"/>
-      <c r="L31" s="70"/>
-      <c r="M31" s="70"/>
-      <c r="N31" s="81"/>
-    </row>
-    <row r="32" ht="22" customHeight="1" spans="2:14">
-      <c r="B32" s="67"/>
-      <c r="C32" s="68"/>
-      <c r="D32" s="69"/>
-      <c r="E32" s="70"/>
-      <c r="F32" s="70"/>
-      <c r="G32" s="70"/>
-      <c r="H32" s="70"/>
-      <c r="I32" s="70"/>
-      <c r="J32" s="70"/>
-      <c r="K32" s="70"/>
-      <c r="L32" s="70"/>
-      <c r="M32" s="70"/>
-      <c r="N32" s="81"/>
-    </row>
-    <row r="33" ht="22" customHeight="1" spans="2:14">
-      <c r="B33" s="71"/>
-      <c r="C33" s="72"/>
-      <c r="D33" s="73"/>
-      <c r="E33" s="74"/>
-      <c r="F33" s="74"/>
-      <c r="G33" s="74"/>
-      <c r="H33" s="74"/>
-      <c r="I33" s="74"/>
-      <c r="J33" s="74"/>
-      <c r="K33" s="74"/>
-      <c r="L33" s="74"/>
-      <c r="M33" s="74"/>
-      <c r="N33" s="82"/>
-    </row>
-    <row r="34" ht="22" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B24:D33"/>
-    <mergeCell ref="E24:N33"/>
-  </mergeCells>
-  <conditionalFormatting sqref="D6">
-    <cfRule type="containsText" dxfId="0" priority="5" operator="between" text="In Progress">
-      <formula>NOT(ISERROR(SEARCH("In Progress",D6)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="4" operator="between" text="Ready to Start">
-      <formula>NOT(ISERROR(SEARCH("Ready to Start",D6)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="3" operator="between" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",D6)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="2" operator="between" text="On Hold">
-      <formula>NOT(ISERROR(SEARCH("On Hold",D6)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="1" operator="between" text="Testing">
-      <formula>NOT(ISERROR(SEARCH("Testing",D6)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6">
-    <cfRule type="containsText" dxfId="5" priority="8" operator="between" text="High">
-      <formula>NOT(ISERROR(SEARCH("High",E6)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="7" operator="between" text="Medium">
-      <formula>NOT(ISERROR(SEARCH("Medium",E6)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="6" operator="between" text="Low">
-      <formula>NOT(ISERROR(SEARCH("Low",E6)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D3:D5">
-    <cfRule type="containsText" dxfId="4" priority="9" operator="between" text="Testing">
-      <formula>NOT(ISERROR(SEARCH("Testing",D3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="10" operator="between" text="On Hold">
-      <formula>NOT(ISERROR(SEARCH("On Hold",D3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="11" operator="between" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",D3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="12" operator="between" text="Ready to Start">
-      <formula>NOT(ISERROR(SEARCH("Ready to Start",D3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="13" operator="between" text="In Progress">
-      <formula>NOT(ISERROR(SEARCH("In Progress",D3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D7:D21">
-    <cfRule type="containsText" dxfId="4" priority="14" operator="between" text="Testing">
-      <formula>NOT(ISERROR(SEARCH("Testing",D7)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="15" operator="between" text="On Hold">
-      <formula>NOT(ISERROR(SEARCH("On Hold",D7)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="16" operator="between" text="Complete">
-      <formula>NOT(ISERROR(SEARCH("Complete",D7)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="17" operator="between" text="Ready to Start">
-      <formula>NOT(ISERROR(SEARCH("Ready to Start",D7)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="18" operator="between" text="In Progress">
-      <formula>NOT(ISERROR(SEARCH("In Progress",D7)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E3:E5;E7:E21">
-    <cfRule type="containsText" dxfId="7" priority="19" operator="between" text="Low">
-      <formula>NOT(ISERROR(SEARCH("Low",E3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="20" operator="between" text="Medium">
-      <formula>NOT(ISERROR(SEARCH("Medium",E3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="21" operator="between" text="High">
-      <formula>NOT(ISERROR(SEARCH("High",E3)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="B1:O34"/>
-  <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="3.33333333333333" customWidth="1"/>
-    <col min="2" max="2" width="15.6666666666667" customWidth="1"/>
-    <col min="3" max="3" width="35.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="22.8333333333333" customWidth="1"/>
-    <col min="5" max="6" width="32.6666666666667" customWidth="1"/>
-    <col min="7" max="7" width="15.6666666666667" customWidth="1"/>
-    <col min="8" max="8" width="12.6666666666667" customWidth="1"/>
-    <col min="9" max="9" width="49.3333333333333" customWidth="1"/>
-    <col min="10" max="10" width="12.6666666666667" customWidth="1"/>
-    <col min="11" max="11" width="24.1666666666667" customWidth="1"/>
-    <col min="12" max="12" width="25.6666666666667" customWidth="1"/>
-    <col min="13" max="13" width="28.5" customWidth="1"/>
-    <col min="14" max="14" width="42.6666666666667" customWidth="1"/>
-    <col min="15" max="15" width="3.33333333333333" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="27.6" spans="2:15">
-      <c r="B1" s="44" t="s">
-        <v>46</v>
-      </c>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="75"/>
-    </row>
-    <row r="2" ht="27.6" spans="2:13">
-      <c r="B2" s="45" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="46" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" s="46" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="47" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="47" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="I2" s="46" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" s="76"/>
-    </row>
-    <row r="3" ht="61" customHeight="1" spans="2:13">
-      <c r="B3" s="48" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="48" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="E3" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3" s="49">
-        <v>46705</v>
-      </c>
-      <c r="G3" s="49">
-        <v>46710</v>
-      </c>
-      <c r="H3" s="50">
-        <v>6</v>
-      </c>
-      <c r="I3" s="48" t="s">
-        <v>50</v>
-      </c>
-      <c r="M3" s="77"/>
-    </row>
-    <row r="4" ht="48" customHeight="1" spans="2:13">
-      <c r="B4" s="48" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="48" t="s">
-        <v>51</v>
-      </c>
-      <c r="D4" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="F4" s="49">
-        <v>46706</v>
-      </c>
-      <c r="G4" s="49">
-        <v>46710</v>
-      </c>
-      <c r="H4" s="50">
-        <v>5</v>
-      </c>
-      <c r="I4" s="48" t="s">
-        <v>52</v>
-      </c>
-      <c r="M4" s="77"/>
-    </row>
-    <row r="5" ht="54" customHeight="1" spans="2:13">
-      <c r="B5" s="48" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="48" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="F5" s="49">
-        <v>46706</v>
-      </c>
-      <c r="G5" s="49">
-        <v>46710</v>
-      </c>
-      <c r="H5" s="50">
-        <v>5</v>
-      </c>
-      <c r="I5" s="48" t="s">
-        <v>54</v>
-      </c>
-      <c r="M5" s="77"/>
-    </row>
-    <row r="6" ht="48" customHeight="1" spans="2:13">
-      <c r="B6" s="48" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="48" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="52">
-        <v>46703</v>
-      </c>
-      <c r="G6" s="52">
-        <v>46709</v>
-      </c>
-      <c r="H6" s="53">
-        <v>7</v>
-      </c>
-      <c r="I6" s="78" t="s">
-        <v>56</v>
-      </c>
-      <c r="M6" s="77"/>
-    </row>
-    <row r="7" ht="47" customHeight="1" spans="2:13">
-      <c r="B7" s="48" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="48" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="36" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="F7" s="55">
-        <v>46708</v>
-      </c>
-      <c r="G7" s="55">
-        <v>46710</v>
-      </c>
-      <c r="H7" s="56">
-        <v>3</v>
-      </c>
-      <c r="I7" s="79" t="s">
-        <v>59</v>
-      </c>
-      <c r="M7" s="77"/>
-    </row>
-    <row r="8" ht="22" customHeight="1" spans="2:13">
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="55"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="77"/>
-      <c r="M8" s="77"/>
-    </row>
-    <row r="9" ht="22" customHeight="1" spans="2:13">
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="77"/>
-      <c r="M9" s="77"/>
-    </row>
-    <row r="10" ht="22" customHeight="1" spans="2:13">
-      <c r="B10" s="54"/>
-      <c r="C10" s="54"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="55"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="56"/>
-      <c r="I10" s="77"/>
-      <c r="M10" s="77"/>
-    </row>
-    <row r="11" ht="22" customHeight="1" spans="2:13">
-      <c r="B11" s="54"/>
-      <c r="C11" s="54"/>
-      <c r="D11" s="57"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="55"/>
-      <c r="G11" s="55"/>
-      <c r="H11" s="56"/>
-      <c r="I11" s="77"/>
-      <c r="M11" s="77"/>
-    </row>
-    <row r="12" ht="22" customHeight="1" spans="2:13">
-      <c r="B12" s="54"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="57"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="77"/>
-      <c r="M12" s="77"/>
-    </row>
-    <row r="13" ht="22" customHeight="1" spans="2:13">
-      <c r="B13" s="54"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="77"/>
-      <c r="M13" s="77"/>
-    </row>
-    <row r="14" ht="22" customHeight="1" spans="2:13">
-      <c r="B14" s="54"/>
-      <c r="C14" s="54"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="56"/>
-      <c r="I14" s="77"/>
-      <c r="M14" s="77"/>
-    </row>
-    <row r="15" ht="22" customHeight="1" spans="2:13">
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="59"/>
-      <c r="G15" s="59"/>
-      <c r="H15" s="56"/>
-      <c r="I15" s="77"/>
-      <c r="M15" s="77"/>
-    </row>
-    <row r="16" ht="22" customHeight="1" spans="2:13">
-      <c r="B16" s="54"/>
-      <c r="C16" s="54"/>
-      <c r="D16" s="57"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="59"/>
-      <c r="G16" s="59"/>
-      <c r="H16" s="56"/>
-      <c r="I16" s="77"/>
-      <c r="M16" s="77"/>
-    </row>
-    <row r="17" ht="22" customHeight="1" spans="2:13">
-      <c r="B17" s="54"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="59"/>
-      <c r="G17" s="59"/>
-      <c r="H17" s="56"/>
-      <c r="I17" s="77"/>
-      <c r="M17" s="77"/>
-    </row>
-    <row r="18" ht="22" customHeight="1" spans="2:13">
-      <c r="B18" s="54"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="59"/>
-      <c r="G18" s="59"/>
-      <c r="H18" s="56"/>
-      <c r="I18" s="77"/>
-      <c r="M18" s="77"/>
-    </row>
-    <row r="19" ht="22" customHeight="1" spans="2:13">
-      <c r="B19" s="54"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="58"/>
-      <c r="F19" s="59"/>
-      <c r="G19" s="59"/>
-      <c r="H19" s="56"/>
-      <c r="I19" s="77"/>
-      <c r="M19" s="77"/>
-    </row>
-    <row r="20" ht="22" customHeight="1" spans="2:13">
-      <c r="B20" s="54"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="57"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="59"/>
-      <c r="G20" s="59"/>
-      <c r="H20" s="56"/>
-      <c r="I20" s="77"/>
-      <c r="M20" s="77"/>
-    </row>
-    <row r="21" ht="22" customHeight="1" spans="2:13">
-      <c r="B21" s="54"/>
-      <c r="C21" s="54"/>
-      <c r="D21" s="57"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="59"/>
-      <c r="G21" s="59"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="77"/>
-      <c r="M21" s="77"/>
-    </row>
-    <row r="22" ht="16.8" spans="2:9">
-      <c r="B22" s="60"/>
-      <c r="C22" s="60"/>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="61"/>
-      <c r="G22" s="61"/>
-      <c r="H22" s="62">
-        <f>MAX(G3:G5)-MIN(F3:F5)+1</f>
-        <v>6</v>
-      </c>
-      <c r="I22" s="60"/>
-    </row>
-    <row r="23" ht="22" customHeight="1"/>
-    <row r="24" ht="45" customHeight="1" spans="2:14">
-      <c r="B24" s="63" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C24" s="64"/>
       <c r="D24" s="65"/>
@@ -17865,52 +17836,52 @@
     <mergeCell ref="E24:N33"/>
   </mergeCells>
   <conditionalFormatting sqref="E6">
-    <cfRule type="containsText" dxfId="5" priority="3" operator="between" text="High">
+    <cfRule type="containsText" dxfId="7" priority="3" operator="between" text="High">
       <formula>NOT(ISERROR(SEARCH("High",E6)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="6" priority="2" operator="between" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",E6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="1" operator="between" text="Low">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="between" text="Low">
       <formula>NOT(ISERROR(SEARCH("Low",E6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E7">
-    <cfRule type="containsText" dxfId="5" priority="6" operator="between" text="High">
+    <cfRule type="containsText" dxfId="7" priority="6" operator="between" text="High">
       <formula>NOT(ISERROR(SEARCH("High",E7)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="6" priority="5" operator="between" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",E7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="4" operator="between" text="Low">
+    <cfRule type="containsText" dxfId="5" priority="4" operator="between" text="Low">
       <formula>NOT(ISERROR(SEARCH("Low",E7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:D21">
-    <cfRule type="containsText" dxfId="4" priority="7" operator="between" text="Testing">
+    <cfRule type="containsText" dxfId="0" priority="7" operator="between" text="Testing">
       <formula>NOT(ISERROR(SEARCH("Testing",D3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="8" operator="between" text="On Hold">
+    <cfRule type="containsText" dxfId="1" priority="8" operator="between" text="On Hold">
       <formula>NOT(ISERROR(SEARCH("On Hold",D3)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="2" priority="9" operator="between" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",D3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="10" operator="between" text="Ready to Start">
+    <cfRule type="containsText" dxfId="3" priority="10" operator="between" text="Ready to Start">
       <formula>NOT(ISERROR(SEARCH("Ready to Start",D3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="11" operator="between" text="In Progress">
+    <cfRule type="containsText" dxfId="4" priority="11" operator="between" text="In Progress">
       <formula>NOT(ISERROR(SEARCH("In Progress",D3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:E5;E8:E21">
-    <cfRule type="containsText" dxfId="7" priority="32" operator="between" text="Low">
+    <cfRule type="containsText" dxfId="5" priority="32" operator="between" text="Low">
       <formula>NOT(ISERROR(SEARCH("Low",E3)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="6" priority="33" operator="between" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",E3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="34" operator="between" text="High">
+    <cfRule type="containsText" dxfId="7" priority="34" operator="between" text="High">
       <formula>NOT(ISERROR(SEARCH("High",E3)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17944,7 +17915,7 @@
   <sheetData>
     <row r="1" ht="27.6" spans="2:15">
       <c r="B1" s="44" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C1" s="44"/>
       <c r="D1" s="44"/>
@@ -17992,25 +17963,25 @@
         <v>37</v>
       </c>
       <c r="C3" s="48" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E3" s="29" t="s">
         <v>35</v>
       </c>
       <c r="F3" s="49">
-        <v>46712</v>
+        <v>46713</v>
       </c>
       <c r="G3" s="49">
-        <v>46718</v>
+        <v>46719</v>
       </c>
       <c r="H3" s="50">
         <v>7</v>
       </c>
       <c r="I3" s="48" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M3" s="77"/>
     </row>
@@ -18019,25 +17990,25 @@
         <v>37</v>
       </c>
       <c r="C4" s="48" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F4" s="49">
-        <v>46715</v>
+        <v>46722</v>
       </c>
       <c r="G4" s="49">
-        <v>46719</v>
+        <v>46724</v>
       </c>
       <c r="H4" s="50">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I4" s="48" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="M4" s="77"/>
     </row>
@@ -18046,25 +18017,25 @@
         <v>37</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F5" s="52">
+        <v>46713</v>
+      </c>
+      <c r="G5" s="52">
         <v>46715</v>
       </c>
-      <c r="G5" s="52">
-        <v>46719</v>
-      </c>
       <c r="H5" s="56">
-        <v>5</v>
-      </c>
-      <c r="I5" s="83" t="s">
-        <v>66</v>
+        <v>3</v>
+      </c>
+      <c r="I5" s="86" t="s">
+        <v>64</v>
       </c>
       <c r="M5" s="77"/>
     </row>
@@ -18073,25 +18044,25 @@
         <v>37</v>
       </c>
       <c r="C6" s="48" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F6" s="52">
         <v>46716</v>
       </c>
       <c r="G6" s="52">
-        <v>46719</v>
+        <v>46717</v>
       </c>
       <c r="H6" s="53">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I6" s="78" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M6" s="77"/>
     </row>
@@ -18100,37 +18071,53 @@
         <v>37</v>
       </c>
       <c r="C7" s="48" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F7" s="55">
-        <v>46718</v>
+        <v>46720</v>
       </c>
       <c r="G7" s="55">
         <v>46721</v>
       </c>
       <c r="H7" s="56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7" s="79" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M7" s="77"/>
     </row>
-    <row r="8" ht="22" customHeight="1" spans="2:13">
-      <c r="B8" s="54"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="55"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="77"/>
+    <row r="8" ht="92" customHeight="1" spans="2:13">
+      <c r="B8" s="83" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="84" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="85" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="49">
+        <v>46722</v>
+      </c>
+      <c r="G8" s="49">
+        <v>46723</v>
+      </c>
+      <c r="H8" s="50">
+        <v>2</v>
+      </c>
+      <c r="I8" s="87" t="s">
+        <v>70</v>
+      </c>
       <c r="M8" s="77"/>
     </row>
     <row r="9" ht="22" customHeight="1" spans="2:13">
@@ -18285,14 +18272,14 @@
       <c r="G22" s="61"/>
       <c r="H22" s="62">
         <f>MAX(G3:G4)-MIN(F3:F4)+1</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I22" s="60"/>
     </row>
     <row r="23" ht="22" customHeight="1"/>
     <row r="24" ht="45" customHeight="1" spans="2:14">
       <c r="B24" s="63" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C24" s="64"/>
       <c r="D24" s="65"/>
@@ -18450,41 +18437,69 @@
     <mergeCell ref="E24:N33"/>
   </mergeCells>
   <conditionalFormatting sqref="E7">
-    <cfRule type="containsText" dxfId="5" priority="3" operator="between" text="High">
+    <cfRule type="containsText" dxfId="7" priority="16" operator="between" text="High">
       <formula>NOT(ISERROR(SEARCH("High",E7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="2" operator="between" text="Medium">
+    <cfRule type="containsText" dxfId="6" priority="15" operator="between" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",E7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="1" operator="between" text="Low">
+    <cfRule type="containsText" dxfId="5" priority="14" operator="between" text="Low">
       <formula>NOT(ISERROR(SEARCH("Low",E7)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D3:D21">
-    <cfRule type="containsText" dxfId="4" priority="7" operator="between" text="Testing">
+  <conditionalFormatting sqref="D8">
+    <cfRule type="containsText" dxfId="4" priority="5" operator="between" text="In Progress">
+      <formula>NOT(ISERROR(SEARCH("In Progress",D8)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="4" operator="between" text="Ready to Start">
+      <formula>NOT(ISERROR(SEARCH("Ready to Start",D8)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="3" operator="between" text="Complete">
+      <formula>NOT(ISERROR(SEARCH("Complete",D8)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="2" operator="between" text="On Hold">
+      <formula>NOT(ISERROR(SEARCH("On Hold",D8)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="1" operator="between" text="Testing">
+      <formula>NOT(ISERROR(SEARCH("Testing",D8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8">
+    <cfRule type="containsText" dxfId="7" priority="13" operator="between" text="High">
+      <formula>NOT(ISERROR(SEARCH("High",E8)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="12" operator="between" text="Medium">
+      <formula>NOT(ISERROR(SEARCH("Medium",E8)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="11" operator="between" text="Low">
+      <formula>NOT(ISERROR(SEARCH("Low",E8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3:D7;D9:D21">
+    <cfRule type="containsText" dxfId="0" priority="20" operator="between" text="Testing">
       <formula>NOT(ISERROR(SEARCH("Testing",D3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="8" operator="between" text="On Hold">
+    <cfRule type="containsText" dxfId="1" priority="21" operator="between" text="On Hold">
       <formula>NOT(ISERROR(SEARCH("On Hold",D3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="9" operator="between" text="Complete">
+    <cfRule type="containsText" dxfId="2" priority="22" operator="between" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",D3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="10" operator="between" text="Ready to Start">
+    <cfRule type="containsText" dxfId="3" priority="23" operator="between" text="Ready to Start">
       <formula>NOT(ISERROR(SEARCH("Ready to Start",D3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="11" operator="between" text="In Progress">
+    <cfRule type="containsText" dxfId="4" priority="24" operator="between" text="In Progress">
       <formula>NOT(ISERROR(SEARCH("In Progress",D3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:E6;E8:E21">
-    <cfRule type="containsText" dxfId="7" priority="4" operator="between" text="Low">
+  <conditionalFormatting sqref="E3:E6;E9:E21">
+    <cfRule type="containsText" dxfId="5" priority="17" operator="between" text="Low">
       <formula>NOT(ISERROR(SEARCH("Low",E3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="5" operator="between" text="Medium">
+    <cfRule type="containsText" dxfId="6" priority="18" operator="between" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",E3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="6" operator="between" text="High">
+    <cfRule type="containsText" dxfId="7" priority="19" operator="between" text="High">
       <formula>NOT(ISERROR(SEARCH("High",E3)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18569,19 +18584,19 @@
         <v>72</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F3" s="49">
         <v>46731</v>
       </c>
       <c r="G3" s="49">
-        <v>46734</v>
+        <v>46732</v>
       </c>
       <c r="H3" s="50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I3" s="48" t="s">
         <v>73</v>
@@ -18596,19 +18611,19 @@
         <v>74</v>
       </c>
       <c r="D4" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E4" s="31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F4" s="49">
         <v>46731</v>
       </c>
       <c r="G4" s="49">
-        <v>46737</v>
+        <v>46732</v>
       </c>
       <c r="H4" s="50">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I4" s="48" t="s">
         <v>75</v>
@@ -18623,19 +18638,19 @@
         <v>76</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F5" s="49">
         <v>46729</v>
       </c>
       <c r="G5" s="49">
-        <v>46733</v>
+        <v>46730</v>
       </c>
       <c r="H5" s="50">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I5" s="48" t="s">
         <v>77</v>
@@ -18650,16 +18665,16 @@
         <v>78</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F6" s="52">
-        <v>46729</v>
+        <v>46731</v>
       </c>
       <c r="G6" s="52">
-        <v>46732</v>
+        <v>46734</v>
       </c>
       <c r="H6" s="53">
         <v>4</v>
@@ -18677,19 +18692,19 @@
         <v>80</v>
       </c>
       <c r="D7" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E7" s="29" t="s">
         <v>35</v>
       </c>
       <c r="F7" s="55">
-        <v>46725</v>
+        <v>46737</v>
       </c>
       <c r="G7" s="55">
-        <v>46731</v>
+        <v>46742</v>
       </c>
       <c r="H7" s="56">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I7" s="79" t="s">
         <v>81</v>
@@ -18704,16 +18719,16 @@
         <v>82</v>
       </c>
       <c r="D8" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F8" s="55">
-        <v>46722</v>
+        <v>46745</v>
       </c>
       <c r="G8" s="55">
-        <v>46725</v>
+        <v>46748</v>
       </c>
       <c r="H8" s="56">
         <v>4</v>
@@ -18723,15 +18738,31 @@
       </c>
       <c r="M8" s="77"/>
     </row>
-    <row r="9" ht="22" customHeight="1" spans="2:13">
-      <c r="B9" s="54"/>
-      <c r="C9" s="54"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="56"/>
-      <c r="I9" s="77"/>
+    <row r="9" ht="54" customHeight="1" spans="2:13">
+      <c r="B9" s="54" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="54" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="55">
+        <v>46751</v>
+      </c>
+      <c r="G9" s="55">
+        <v>46756</v>
+      </c>
+      <c r="H9" s="56">
+        <v>6</v>
+      </c>
+      <c r="I9" s="79" t="s">
+        <v>85</v>
+      </c>
       <c r="M9" s="77"/>
     </row>
     <row r="10" ht="22" customHeight="1" spans="2:13">
@@ -18875,14 +18906,14 @@
       <c r="G22" s="61"/>
       <c r="H22" s="62">
         <f>MAX(G3:G5)-MIN(F3:F5)+1</f>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I22" s="60"/>
     </row>
     <row r="23" ht="22" customHeight="1"/>
     <row r="24" ht="45" customHeight="1" spans="2:14">
       <c r="B24" s="63" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C24" s="64"/>
       <c r="D24" s="65"/>
@@ -19040,41 +19071,52 @@
     <mergeCell ref="E24:N33"/>
   </mergeCells>
   <conditionalFormatting sqref="E7">
-    <cfRule type="containsText" dxfId="5" priority="3" operator="between" text="High">
+    <cfRule type="containsText" dxfId="7" priority="6" operator="between" text="High">
       <formula>NOT(ISERROR(SEARCH("High",E7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="2" operator="between" text="Medium">
+    <cfRule type="containsText" dxfId="6" priority="5" operator="between" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",E7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="1" operator="between" text="Low">
+    <cfRule type="containsText" dxfId="5" priority="4" operator="between" text="Low">
       <formula>NOT(ISERROR(SEARCH("Low",E7)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E9">
+    <cfRule type="containsText" dxfId="7" priority="3" operator="between" text="High">
+      <formula>NOT(ISERROR(SEARCH("High",E9)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="2" operator="between" text="Medium">
+      <formula>NOT(ISERROR(SEARCH("Medium",E9)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="1" operator="between" text="Low">
+      <formula>NOT(ISERROR(SEARCH("Low",E9)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D3:D21">
-    <cfRule type="containsText" dxfId="4" priority="15" operator="between" text="Testing">
+    <cfRule type="containsText" dxfId="0" priority="18" operator="between" text="Testing">
       <formula>NOT(ISERROR(SEARCH("Testing",D3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="16" operator="between" text="On Hold">
+    <cfRule type="containsText" dxfId="1" priority="19" operator="between" text="On Hold">
       <formula>NOT(ISERROR(SEARCH("On Hold",D3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="17" operator="between" text="Complete">
+    <cfRule type="containsText" dxfId="2" priority="20" operator="between" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",D3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="18" operator="between" text="Ready to Start">
+    <cfRule type="containsText" dxfId="3" priority="21" operator="between" text="Ready to Start">
       <formula>NOT(ISERROR(SEARCH("Ready to Start",D3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="19" operator="between" text="In Progress">
+    <cfRule type="containsText" dxfId="4" priority="22" operator="between" text="In Progress">
       <formula>NOT(ISERROR(SEARCH("In Progress",D3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:E6;E8:E21">
-    <cfRule type="containsText" dxfId="7" priority="4" operator="between" text="Low">
+  <conditionalFormatting sqref="E3:E6;E8;E10:E21">
+    <cfRule type="containsText" dxfId="5" priority="7" operator="between" text="Low">
       <formula>NOT(ISERROR(SEARCH("Low",E3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="5" operator="between" text="Medium">
+    <cfRule type="containsText" dxfId="6" priority="8" operator="between" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",E3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="6" operator="between" text="High">
+    <cfRule type="containsText" dxfId="7" priority="9" operator="between" text="High">
       <formula>NOT(ISERROR(SEARCH("High",E3)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19101,7 +19143,7 @@
     <row r="1" customHeight="1" spans="1:7">
       <c r="A1" s="2"/>
       <c r="B1" s="19" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C1" s="19"/>
       <c r="D1" s="19"/>
@@ -19121,11 +19163,11 @@
     <row r="3" spans="1:7">
       <c r="A3" s="5"/>
       <c r="B3" s="24" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C3" s="25"/>
       <c r="D3" s="24" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E3" s="26"/>
       <c r="F3" s="27"/>
@@ -19147,7 +19189,7 @@
     <row r="5" spans="1:7">
       <c r="A5" s="5"/>
       <c r="B5" s="31" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C5" s="25"/>
       <c r="D5" s="31" t="s">
@@ -19160,11 +19202,11 @@
     <row r="6" ht="22" customHeight="1" spans="1:7">
       <c r="A6" s="5"/>
       <c r="B6" s="31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C6" s="25"/>
       <c r="D6" s="31" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E6" s="26"/>
       <c r="F6" s="32"/>
@@ -19175,7 +19217,7 @@
       <c r="B7" s="33"/>
       <c r="C7" s="25"/>
       <c r="D7" s="34" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E7" s="26"/>
       <c r="F7" s="30"/>
@@ -19186,7 +19228,7 @@
       <c r="B8" s="33"/>
       <c r="C8" s="25"/>
       <c r="D8" s="35" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E8" s="26"/>
       <c r="F8" s="30"/>
@@ -19197,7 +19239,7 @@
       <c r="B9" s="25"/>
       <c r="C9" s="25"/>
       <c r="D9" s="36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E9" s="26"/>
       <c r="F9" s="37"/>
@@ -19284,13 +19326,13 @@
     <mergeCell ref="B1:E2"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:B6">
-    <cfRule type="containsText" dxfId="7" priority="6" operator="between" text="Low">
+    <cfRule type="containsText" dxfId="5" priority="6" operator="between" text="Low">
       <formula>NOT(ISERROR(SEARCH("Low",B4)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="6" priority="7" operator="between" text="Medium">
       <formula>NOT(ISERROR(SEARCH("Medium",B4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="8" operator="between" text="High">
+    <cfRule type="containsText" dxfId="7" priority="8" operator="between" text="High">
       <formula>NOT(ISERROR(SEARCH("High",B4)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19312,36 +19354,36 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4:D9">
-    <cfRule type="containsText" dxfId="4" priority="1" operator="between" text="Testing">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="between" text="Testing">
       <formula>NOT(ISERROR(SEARCH("Testing",D4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="2" operator="between" text="On Hold">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="between" text="On Hold">
       <formula>NOT(ISERROR(SEARCH("On Hold",D4)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="2" priority="3" operator="between" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",D4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="4" operator="between" text="Ready to Start">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="between" text="Ready to Start">
       <formula>NOT(ISERROR(SEARCH("Ready to Start",D4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="5" operator="between" text="In Progress">
+    <cfRule type="containsText" dxfId="4" priority="5" operator="between" text="In Progress">
       <formula>NOT(ISERROR(SEARCH("In Progress",D4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F9">
-    <cfRule type="containsText" dxfId="4" priority="9" operator="between" text="Testing">
+    <cfRule type="containsText" dxfId="0" priority="9" operator="between" text="Testing">
       <formula>NOT(ISERROR(SEARCH("Testing",F4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="10" operator="between" text="On Hold">
+    <cfRule type="containsText" dxfId="1" priority="10" operator="between" text="On Hold">
       <formula>NOT(ISERROR(SEARCH("On Hold",F4)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="2" priority="11" operator="between" text="Complete">
       <formula>NOT(ISERROR(SEARCH("Complete",F4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="12" operator="between" text="Ready to Start">
+    <cfRule type="containsText" dxfId="3" priority="12" operator="between" text="Ready to Start">
       <formula>NOT(ISERROR(SEARCH("Ready to Start",F4)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="13" operator="between" text="In Progress">
+    <cfRule type="containsText" dxfId="4" priority="13" operator="between" text="In Progress">
       <formula>NOT(ISERROR(SEARCH("In Progress",F4)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19372,7 +19414,7 @@
     <row r="2" ht="27.6" spans="1:5">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -19409,11 +19451,11 @@
     <row r="7" ht="16.8" spans="1:5">
       <c r="A7" s="5"/>
       <c r="B7" s="12" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C7" s="11"/>
       <c r="D7" s="12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E7" s="9"/>
     </row>
